--- a/GPU_Memory.xlsx
+++ b/GPU_Memory.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowWidth="20850" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario1" sheetId="1" r:id="rId1"/>
@@ -224,7 +224,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="62">
   <si>
     <t xml:space="preserve">hidden dim d = 256
 layers L = 24
@@ -234,6 +234,27 @@
 dtype BF16 = 2 字节 </t>
   </si>
   <si>
+    <t>dim</t>
+  </si>
+  <si>
+    <t>Layer</t>
+  </si>
+  <si>
+    <t>Head</t>
+  </si>
+  <si>
+    <t>Seq</t>
+  </si>
+  <si>
+    <t>Batch</t>
+  </si>
+  <si>
+    <t>BF16</t>
+  </si>
+  <si>
+    <t>Vocab</t>
+  </si>
+  <si>
     <t>- 词嵌入层 ：6400 × 256 = 1,638,400
 - 注意力机制 ：每层约 262,144 参数，24层约 6,291,456
 - 前馈网络 ：每层约 539,136 参数，24层约 12,939,264
@@ -249,27 +270,6 @@
     <t>实际  41.054M</t>
   </si>
   <si>
-    <t>dim</t>
-  </si>
-  <si>
-    <t>Layer</t>
-  </si>
-  <si>
-    <t>Head</t>
-  </si>
-  <si>
-    <t>Seq</t>
-  </si>
-  <si>
-    <t>Batch</t>
-  </si>
-  <si>
-    <t>BF16</t>
-  </si>
-  <si>
-    <t>Vocab</t>
-  </si>
-  <si>
     <t>1.模型参数</t>
   </si>
   <si>
@@ -288,7 +288,7 @@
     <t>L*4DD</t>
   </si>
   <si>
-    <t>1.1 词表 （词嵌入层参数）</t>
+    <t>1.1 词表 （词嵌入层参数）+   ROPE</t>
   </si>
   <si>
     <t>Q/K/V 权重</t>
@@ -362,7 +362,7 @@
     <t>BHSS</t>
   </si>
   <si>
-    <t>1.3 最终归一化层</t>
+    <t>1.4 最终归一化层</t>
   </si>
   <si>
     <t>2.2 FFN 层激活张量</t>
@@ -401,10 +401,20 @@
     <t>7571MiB /   8188MiB |</t>
   </si>
   <si>
+    <t>512
+-8192</t>
+  </si>
+  <si>
     <t>Head_H</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FFF48CCA"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>6623</t>
     </r>
     <r>
@@ -1139,7 +1149,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1174,11 +1184,20 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1189,6 +1208,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
@@ -1505,7 +1530,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="27.7272727272727" customWidth="1"/>
@@ -1520,64 +1545,106 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" ht="42" spans="1:9">
+      <c r="B2" s="2">
+        <v>256</v>
+      </c>
+      <c r="C2" s="2">
+        <v>24</v>
+      </c>
+      <c r="D2" s="2">
+        <v>16</v>
+      </c>
+      <c r="E2" s="2">
+        <v>512</v>
+      </c>
+      <c r="F2" s="2">
+        <v>32</v>
+      </c>
+      <c r="G2" s="2">
+        <v>2</v>
+      </c>
+      <c r="H2" s="10">
+        <v>6400</v>
+      </c>
       <c r="I2" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="I3" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="2">
-        <v>256</v>
+      <c r="A5" s="12">
+        <v>1024</v>
       </c>
       <c r="B5" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2">
         <v>16</v>
       </c>
       <c r="D5" s="2">
-        <v>512</v>
+        <v>256000</v>
       </c>
       <c r="E5" s="2">
         <v>32</v>
       </c>
       <c r="F5" s="2">
-        <v>2</v>
-      </c>
-      <c r="G5" s="10">
-        <v>6400</v>
+        <v>1</v>
+      </c>
+      <c r="G5" s="11">
+        <v>248320</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1590,12 +1657,12 @@
       <c r="C9" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="14">
         <f>SUM(H10:H21)</f>
-        <v>39.89892578125</v>
+        <v>733.789306640625</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1604,21 +1671,21 @@
       </c>
       <c r="B10" s="5">
         <f>SUM(B11:B16)/1024/1024*F5</f>
-        <v>1.5009765625</v>
+        <v>12.001953125</v>
       </c>
       <c r="C10" s="5">
         <f>B10*B5</f>
-        <v>36.0234375</v>
+        <v>240.0390625</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="15" t="s">
         <v>17</v>
       </c>
       <c r="H10" s="5">
-        <f>G5*A5/1024/1024*F5</f>
-        <v>3.125</v>
+        <f>G5*A5/1024/1024*F5+D5*A5*F5/1024/1024</f>
+        <v>492.5</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1627,13 +1694,13 @@
       </c>
       <c r="B11" s="4">
         <f>3*A5*A5</f>
-        <v>196608</v>
+        <v>3145728</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="15" t="s">
         <v>20</v>
       </c>
       <c r="H11" s="5"/>
@@ -1644,18 +1711,18 @@
       </c>
       <c r="B12" s="4">
         <f>1*A5*A5</f>
-        <v>65536</v>
+        <v>1048576</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="15" t="s">
         <v>23</v>
       </c>
       <c r="H12" s="5">
         <f>A5*B5/1024/1024*F5</f>
-        <v>0.01171875</v>
+        <v>0.01953125</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1664,15 +1731,15 @@
       </c>
       <c r="B13" s="4">
         <f>A5*2</f>
-        <v>512</v>
+        <v>2048</v>
       </c>
       <c r="C13" s="5"/>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="15" t="s">
         <v>25</v>
       </c>
       <c r="H13" s="5">
-        <f>4*A5*A5*B5/1024/1024*2</f>
-        <v>12</v>
+        <f>4*A5*A5*B5/1024/1024*F5</f>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1681,22 +1748,22 @@
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="5"/>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="15" t="s">
         <v>27</v>
       </c>
       <c r="H14" s="5">
         <f>A5*B5/1024/1024*F5</f>
-        <v>0.01171875</v>
+        <v>0.01953125</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="4"/>
       <c r="B15" s="4">
         <f>A5*4*A5</f>
-        <v>262144</v>
+        <v>4194304</v>
       </c>
       <c r="C15" s="5"/>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="15" t="s">
         <v>28</v>
       </c>
       <c r="H15" s="5"/>
@@ -1705,17 +1772,17 @@
       <c r="A16" s="4"/>
       <c r="B16" s="4">
         <f>4*A5*A5</f>
-        <v>262144</v>
+        <v>4194304</v>
       </c>
       <c r="C16" s="5"/>
-      <c r="G16" s="13" t="s">
+      <c r="G16" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="17">
         <f>A5*CEILING(A5*8/3,64)*B5*F5/1024/1024</f>
-        <v>8.25</v>
-      </c>
-      <c r="I16" s="17" t="s">
+        <v>53.75</v>
+      </c>
+      <c r="I16" s="22" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1725,12 +1792,12 @@
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="17">
         <f>CEILING(A5*8/3,64)*A5*B5*F5/1024/1024</f>
-        <v>8.25</v>
+        <v>53.75</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1739,18 +1806,18 @@
       </c>
       <c r="B18" s="6">
         <f>SUM(B19:B21)/1024/1024*F5</f>
-        <v>288</v>
+        <v>32032000</v>
       </c>
       <c r="C18" s="6">
         <f>B18*B5</f>
-        <v>6912</v>
-      </c>
-      <c r="G18" s="13" t="s">
+        <v>640640000</v>
+      </c>
+      <c r="G18" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="15">
+      <c r="H18" s="18">
         <f>A5*CEILING(A5*8/3,64)*B5*F5/1024/1024</f>
-        <v>8.25</v>
+        <v>53.75</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1759,13 +1826,13 @@
       </c>
       <c r="B19" s="6">
         <f>E5*D5*A5*3</f>
-        <v>12582912</v>
+        <v>25165824000</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" t="s">
         <v>36</v>
       </c>
-      <c r="G19" s="11"/>
+      <c r="G19" s="15"/>
       <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8">
@@ -1774,33 +1841,33 @@
       </c>
       <c r="B20" s="6">
         <f>E5*D5*A5</f>
-        <v>4194304</v>
+        <v>8388608000</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" t="s">
         <v>38</v>
       </c>
-      <c r="G20" s="11"/>
+      <c r="G20" s="15"/>
       <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="19">
         <f>E5*C5*D5*D5</f>
-        <v>134217728</v>
+        <v>33554432000000</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" t="s">
         <v>40</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="G21" s="15" t="s">
         <v>41</v>
       </c>
       <c r="H21" s="5">
         <f>256/1024/1024*F5</f>
-        <v>0.00048828125</v>
+        <v>0.000244140625</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1809,13 +1876,13 @@
       </c>
       <c r="B22" s="6">
         <f>SUM(B23:B24)*F5/1024/1024</f>
-        <v>40</v>
+        <v>40000</v>
       </c>
       <c r="C22" s="6">
         <f>B22*B5</f>
-        <v>960</v>
-      </c>
-      <c r="G22" s="11"/>
+        <v>800000</v>
+      </c>
+      <c r="G22" s="15"/>
       <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8">
@@ -1824,13 +1891,13 @@
       </c>
       <c r="B23" s="6">
         <f>E5*D5*4*A5</f>
-        <v>16777216</v>
+        <v>33554432000</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" t="s">
         <v>44</v>
       </c>
-      <c r="G23" s="11"/>
+      <c r="G23" s="15"/>
       <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8">
@@ -1839,13 +1906,13 @@
       </c>
       <c r="B24" s="6">
         <f>E5*D5*A5</f>
-        <v>4194304</v>
+        <v>8388608000</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" t="s">
         <v>46</v>
       </c>
-      <c r="G24" s="11"/>
+      <c r="G24" s="15"/>
       <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:8">
@@ -1854,7 +1921,7 @@
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
-      <c r="G25" s="11"/>
+      <c r="G25" s="15"/>
       <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8">
@@ -1864,9 +1931,9 @@
       <c r="B26" s="7"/>
       <c r="C26" s="8">
         <f>1*C10</f>
-        <v>36.0234375</v>
-      </c>
-      <c r="G26" s="11"/>
+        <v>240.0390625</v>
+      </c>
+      <c r="G26" s="15"/>
       <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:8">
@@ -1876,9 +1943,9 @@
       <c r="B27" s="7"/>
       <c r="C27" s="8">
         <f>2*C10</f>
-        <v>72.046875</v>
-      </c>
-      <c r="G27" s="11"/>
+        <v>480.078125</v>
+      </c>
+      <c r="G27" s="15"/>
       <c r="H27" s="5"/>
     </row>
     <row r="28" spans="1:8">
@@ -1890,7 +1957,7 @@
         <f>200</f>
         <v>200</v>
       </c>
-      <c r="G28" s="11"/>
+      <c r="G28" s="15"/>
       <c r="H28" s="5"/>
     </row>
     <row r="29" spans="1:8">
@@ -1900,9 +1967,9 @@
       <c r="B29" s="7"/>
       <c r="C29" s="7">
         <f>SUM(C10:C28)</f>
-        <v>8216.09375</v>
-      </c>
-      <c r="G29" s="11"/>
+        <v>641441160.15625</v>
+      </c>
+      <c r="G29" s="15"/>
       <c r="H29" s="5"/>
     </row>
     <row r="31" spans="1:8">
@@ -1911,6 +1978,52 @@
       </c>
       <c r="C31" t="s">
         <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" ht="28" spans="1:7">
+      <c r="A38" s="12">
+        <v>1024</v>
+      </c>
+      <c r="B38" s="2">
+        <v>20</v>
+      </c>
+      <c r="C38" s="2">
+        <v>16</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" s="2">
+        <v>32</v>
+      </c>
+      <c r="F38" s="2">
+        <v>1</v>
+      </c>
+      <c r="G38" s="21">
+        <v>248320</v>
       </c>
     </row>
   </sheetData>
@@ -1939,22 +2052,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2210,7 +2323,7 @@
     </row>
     <row r="31" ht="26" spans="1:4">
       <c r="C31" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -2239,22 +2352,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2510,7 +2623,7 @@
     </row>
     <row r="31" ht="26" spans="1:4">
       <c r="C31" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -2540,22 +2653,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2815,7 +2928,7 @@
     </row>
     <row r="31" ht="26" spans="1:6">
       <c r="C31" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -2846,22 +2959,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2965,7 +3078,7 @@
       </c>
       <c r="C15" s="5"/>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2976,7 +3089,7 @@
       </c>
       <c r="C16" s="5"/>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -3126,7 +3239,7 @@
     </row>
     <row r="31" ht="26" spans="1:4">
       <c r="C31" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3157,22 +3270,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3428,7 +3541,7 @@
     </row>
     <row r="31" ht="26" spans="1:4">
       <c r="C31" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
